--- a/output/pdf_financials_xlsx/GRB.xlsx
+++ b/output/pdf_financials_xlsx/GRB.xlsx
@@ -5157,46 +5157,46 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.059981</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.038624</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.349883</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.798212</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.296263</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.545209</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.776969</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.161019</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.70376</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.701567</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>7.797368</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>7.797368</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>9.228019</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>9.94862</v>
       </c>
     </row>
     <row r="93">
@@ -9100,7 +9100,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -11352,7 +11356,11 @@
           <t>Reserves 13 9,228,019</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -12960,7 +12968,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -18648,7 +18660,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -20026,7 +20042,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -22860,7 +22880,11 @@
           <t>Warrants reserve 13</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -24404,7 +24428,11 @@
           <t>Warrants reserve 12</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -25182,7 +25210,11 @@
           <t>Warrants reserve 11</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E212" s="5" t="n">
         <v>0.059981</v>
       </c>

--- a/output/pdf_financials_xlsx/GRB.xlsx
+++ b/output/pdf_financials_xlsx/GRB.xlsx
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.005027</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.014813</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.01608</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0.017534</v>
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.033887</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.029933</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -1886,13 +1886,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.149788</v>
+        <v>-0.154815</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.041563</v>
+        <v>-1.056376</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.577361</v>
+        <v>-1.593441</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.133008</v>
@@ -1922,10 +1922,10 @@
         <v>-9.325226000000001</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-6.574638</v>
+        <v>-6.608525</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.525965</v>
+        <v>-1.555898</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-1.525965</v>
@@ -1996,13 +1996,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.149788</v>
+        <v>-0.154815</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.041563</v>
+        <v>-1.056376</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.577361</v>
+        <v>-1.593441</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.133008</v>
@@ -2032,10 +2032,10 @@
         <v>-9.325226000000001</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-6.574638</v>
+        <v>-6.608525</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.525965</v>
+        <v>-1.555898</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-1.525965</v>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.652962</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.22858</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.003184</v>
@@ -2282,31 +2282,31 @@
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000132</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.002695</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.025865</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.047672</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.009273</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.02495</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.02495</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.047098</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.057539</v>
       </c>
     </row>
     <row r="35">
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.652962</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.22858</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.003184</v>
@@ -2380,31 +2380,31 @@
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000132</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1.06875</v>
+        <v>1.071445</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3.152813</v>
+        <v>3.178678</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>2.9925</v>
+        <v>3.040172</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.454219</v>
+        <v>0.463492</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>1.8198</v>
+        <v>1.84475</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>1.8198</v>
+        <v>1.84475</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>1.755</v>
+        <v>1.802098</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>3.096</v>
+        <v>3.153539</v>
       </c>
     </row>
     <row r="37">
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.794112</v>
+        <v>0.14115</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.382219</v>
+        <v>0.153639</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.183405</v>
@@ -2968,19 +2968,19 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.717011</v>
+        <v>0.716879</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.007311</v>
+        <v>0.004616</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.029445</v>
+        <v>0.00358</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.097327</v>
+        <v>0.049655</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.071395</v>
+        <v>0.062122</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
@@ -2989,10 +2989,10 @@
         <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.030936</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.124114</v>
+        <v>0.066575</v>
       </c>
     </row>
     <row r="49">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -23222,7 +23222,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E189" s="5" t="n">
@@ -51030,7 +51030,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
@@ -52556,7 +52556,7 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -69070,7 +69070,7 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
@@ -69826,7 +69826,7 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
@@ -70584,7 +70584,7 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E749" s="5" t="n">

--- a/output/pdf_financials_xlsx/GRB.xlsx
+++ b/output/pdf_financials_xlsx/GRB.xlsx
@@ -3940,19 +3940,19 @@
         <v>0</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>1.01493</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>4.147032</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>2.722357</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>2.141336</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>1.875924</v>
       </c>
       <c r="O67" s="3" t="n">
         <v>0</v>
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.015148</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001101</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0</v>
@@ -5855,43 +5855,43 @@
         <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.454018</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.6660239999999999</v>
       </c>
       <c r="E107" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>0.120303</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>0.6942160000000001</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>0.390002</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>0.821427</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>0.990448</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>0.954465</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>1.17619</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>0.334534</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>0.236922</v>
       </c>
     </row>
     <row r="108">
@@ -6219,7 +6219,7 @@
         <v>0</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0</v>
+        <v>-0.073784</v>
       </c>
       <c r="K114" s="3" t="n">
         <v>0</v>
@@ -6268,13 +6268,13 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.072658</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.722393</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>0</v>
@@ -25630,7 +25630,11 @@
           <t>Share-based payment expense 12</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -28134,7 +28138,11 @@
           <t>Warrants issued on private placement</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -29504,7 +29512,11 @@
           <t>Share-based payment expense 13</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -30832,7 +30844,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -34998,7 +35014,11 @@
           <t>Proceeds on sale of marketable securities 7</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -36008,7 +36028,11 @@
           <t>Purchase of marketable securities 7</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -36094,7 +36118,11 @@
           <t>Proceeds from sales marketable securities 7</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -37380,7 +37408,11 @@
           <t>Purchase of marketable securities 6</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -37466,7 +37498,11 @@
           <t>Proceeds from sales marketable securities 6</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -38064,7 +38100,11 @@
           <t>Share-based payment expense 14</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
@@ -39512,7 +39552,11 @@
           <t>Share-based payment expense 15</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
@@ -41660,7 +41704,11 @@
           <t>Share-based payment expense</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E407" t="inlineStr">
         <is>
           <t>-</t>
@@ -42856,7 +42904,11 @@
           <t>Share-based payment expense</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E421" t="inlineStr">
         <is>
           <t>-</t>
@@ -44136,7 +44188,11 @@
           <t>Share-based compensation expense 13</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
           <t>-</t>
@@ -45874,7 +45930,11 @@
           <t>Share-based compensation expense 11(d)</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
@@ -46210,7 +46270,11 @@
           <t>Share-based compensation expense 10c</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E461" t="inlineStr">
         <is>
           <t>-</t>
@@ -46296,7 +46360,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E462" s="5" t="n">
         <v>0.015148</v>
       </c>
